--- a/labs/lab-12-secure-a-finance-agent-for-pdpa-and-human-oversight/northstar-agent-security-starter.xlsx
+++ b/labs/lab-12-secure-a-finance-agent-for-pdpa-and-human-oversight/northstar-agent-security-starter.xlsx
@@ -30,7 +30,7 @@
     <t>Course</t>
   </si>
   <si>
-    <t>Generative AI for Finance and Fintech (TGS-2026065050)</t>
+    <t>Microsoft Copilot for Finance (TGS-2026065050)</t>
   </si>
   <si>
     <t>TSC mapping</t>
